--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484326_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484326_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1712</v>
+        <v>7.7124</v>
       </c>
       <c r="E2" t="n">
-        <v>2.622</v>
+        <v>2.9452</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5493</v>
+        <v>4.7672</v>
       </c>
       <c r="G2" t="n">
         <v>5.2817</v>
@@ -610,13 +610,13 @@
         <v>2.7348</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8452</v>
+        <v>-0.3041</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5777</v>
+        <v>-0.2544</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2676</v>
+        <v>-0.0497</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.967</v>
+        <v>6.8467</v>
       </c>
       <c r="E3" t="n">
-        <v>0.309</v>
+        <v>0.7333</v>
       </c>
       <c r="F3" t="n">
-        <v>6.658</v>
+        <v>6.1133</v>
       </c>
       <c r="G3" t="n">
         <v>5.0715</v>
@@ -688,13 +688,13 @@
         <v>3.9069</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.245</v>
+        <v>-0.3653</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8114</v>
+        <v>-0.387</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5664</v>
+        <v>0.0217</v>
       </c>
       <c r="V3" t="n">
         <v>1.1638</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.5527</v>
+        <v>6.4522</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2109</v>
+        <v>0.7563</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3419</v>
+        <v>5.6959</v>
       </c>
       <c r="G4" t="n">
         <v>0.7095</v>
@@ -766,13 +766,13 @@
         <v>4.1022</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2386</v>
+        <v>-0.3391</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5556</v>
+        <v>-0.0101</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6831</v>
+        <v>-0.329</v>
       </c>
       <c r="V4" t="n">
         <v>3.9331</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1953</v>
+        <v>5.3975</v>
       </c>
       <c r="E5" t="n">
-        <v>1.561</v>
+        <v>1.7633</v>
       </c>
       <c r="F5" t="n">
         <v>3.6343</v>
@@ -844,10 +844,10 @@
         <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1156</v>
+        <v>0.0866</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1073</v>
+        <v>0.095</v>
       </c>
       <c r="U5" t="n">
         <v>-0.0083</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6978</v>
+        <v>1.8293</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6617</v>
+        <v>-1.0979</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0361</v>
+        <v>2.9272</v>
       </c>
       <c r="G6" t="n">
         <v>0.4626</v>
@@ -922,13 +922,13 @@
         <v>2.3441</v>
       </c>
       <c r="S6" t="n">
-        <v>2.145</v>
+        <v>0.2765</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2949</v>
+        <v>0.5353</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1498</v>
+        <v>-0.2588</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2772</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>A. DE LA PAZ GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6463</v>
+        <v>0.4622</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9299</v>
+        <v>0.675</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5762</v>
+        <v>-0.2128</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1368</v>
+        <v>0.3597</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1998</v>
+        <v>0.6296</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3366</v>
+        <v>-0.2698</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4708</v>
+        <v>0.6344</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6731</v>
+        <v>0.6344</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2023</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6075</v>
+        <v>-0.2747</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4733</v>
+        <v>-0.0049</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1342</v>
+        <v>-0.2698</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.9301</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7252</v>
+        <v>-0.0929</v>
       </c>
       <c r="T7" t="n">
-        <v>0.71</v>
+        <v>0.0406</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0152</v>
+        <v>-0.1335</v>
       </c>
       <c r="V7" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2222</v>
+        <v>0.3839</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1731</v>
+        <v>-1.0115</v>
       </c>
       <c r="F8" t="n">
         <v>1.3953</v>
@@ -1078,10 +1078,10 @@
         <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2834</v>
+        <v>-0.1218</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4842</v>
+        <v>-0.3225</v>
       </c>
       <c r="U8" t="n">
         <v>0.2008</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DE LA PAZ GONZALEZ</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1584</v>
+        <v>0.2079</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4529</v>
+        <v>-3.3956</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2945</v>
+        <v>3.6034</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3597</v>
+        <v>0.1368</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6296</v>
+        <v>-0.1998</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2698</v>
+        <v>0.3366</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6344</v>
+        <v>-1.4708</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6344</v>
+        <v>-1.6731</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.2023</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2747</v>
+        <v>1.6075</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0049</v>
+        <v>1.4733</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2698</v>
+        <v>0.1342</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.8836</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3967</v>
+        <v>0.2868</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1816</v>
+        <v>0.2443</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2152</v>
+        <v>0.0425</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5621</v>
+        <v>-0.8482</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9814</v>
+        <v>-1.213</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4193</v>
+        <v>0.3648</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3754</v>
@@ -1234,13 +1234,13 @@
         <v>2.3441</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3707</v>
+        <v>-0.6569</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8941</v>
+        <v>-0.1257</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4767</v>
+        <v>-0.5311</v>
       </c>
       <c r="V10" t="n">
         <v>-2.16</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8716</v>
+        <v>-1.2238</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5119</v>
+        <v>-1.9458</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6403</v>
+        <v>0.722</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6702</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1781</v>
+        <v>-0.5303</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5915</v>
+        <v>-0.0254</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5867</v>
+        <v>-0.5049</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0884</v>
+        <v>-1.8367</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.449</v>
+        <v>-3.4696</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3605</v>
+        <v>1.6329</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4814</v>
@@ -1390,13 +1390,13 @@
         <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.154</v>
+        <v>0.0977</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2037</v>
+        <v>0.183</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3577</v>
+        <v>-0.0854</v>
       </c>
       <c r="V12" t="n">
         <v>1.3283</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2152</v>
+        <v>-1.9966</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1022</v>
+        <v>-3.5567</v>
       </c>
       <c r="F13" t="n">
-        <v>1.887</v>
+        <v>1.5602</v>
       </c>
       <c r="G13" t="n">
         <v>-2.5399</v>
@@ -1468,13 +1468,13 @@
         <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1795</v>
+        <v>0.0391</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8335</v>
+        <v>-0.2881</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6541</v>
+        <v>0.3272</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2772</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.8736</v>
+        <v>23.3868</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.33</v>
+        <v>-8.817</v>
       </c>
       <c r="F14" t="n">
         <v>32.2037</v>
@@ -1546,13 +1546,13 @@
         <v>21.4876</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.1366</v>
+        <v>-1.6237</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.8283</v>
+        <v>-0.3150000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3086</v>
+        <v>-1.3085</v>
       </c>
       <c r="V14" t="n">
         <v>6.757400000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1643</v>
+        <v>3.6084</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4756</v>
+        <v>0.06</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6887</v>
+        <v>3.5485</v>
       </c>
       <c r="G15" t="n">
         <v>3.0502</v>
@@ -1624,13 +1624,13 @@
         <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>3.0787</v>
+        <v>1.5229</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9593</v>
+        <v>0.5437</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1195</v>
+        <v>0.9792</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5507</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.819</v>
+        <v>-0.0767</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.7221</v>
+        <v>-1.4213</v>
       </c>
       <c r="F16" t="n">
-        <v>3.9031</v>
+        <v>1.3447</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.2664</v>
+        <v>0.5053</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6501</v>
+        <v>0.4249</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.6163</v>
+        <v>0.0803</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.1802</v>
+        <v>-0.1634</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.8906</v>
+        <v>-0.2443</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.2896</v>
+        <v>0.0809</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.6687</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2405</v>
+        <v>0.6692</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6733</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.9069</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.2743</v>
+        <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>3.6984</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7406</v>
+        <v>-0.0859</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9577</v>
+        <v>0.1719</v>
       </c>
       <c r="V16" t="n">
-        <v>3.6559</v>
+        <v>-0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>2.9917</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8532</v>
+        <v>-0.5813</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9269</v>
+        <v>-2.3286</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0737</v>
+        <v>1.7473</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5053</v>
+        <v>0.5185</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4249</v>
+        <v>-1.4904</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0803</v>
+        <v>2.0089</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1634</v>
+        <v>-0.1958</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2443</v>
+        <v>-1.5311</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0809</v>
+        <v>1.3354</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6687</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6692</v>
+        <v>0.0407</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.6735</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6906</v>
+        <v>0.8612</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5915</v>
+        <v>0.3675</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.4937</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2772</v>
+        <v>-2.547</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-1.3283</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>P. RAMOS SAINZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9456</v>
+        <v>-0.8838</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5308</v>
+        <v>-2.7672</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5853</v>
+        <v>1.8834</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5185</v>
+        <v>-0.5675</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4904</v>
+        <v>-0.1095</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0089</v>
+        <v>-0.458</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1958</v>
+        <v>-1.1661</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5311</v>
+        <v>-0.9785</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3354</v>
+        <v>-0.1875</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.5986</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0407</v>
+        <v>0.869</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6735</v>
+        <v>-0.2704</v>
       </c>
       <c r="P18" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4969</v>
+        <v>-0.3164</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1653</v>
+        <v>-0.4291</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3316</v>
+        <v>0.1127</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.547</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.3283</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7758</v>
+        <v>-1.981</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1717</v>
+        <v>-2.2146</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3958</v>
+        <v>0.2335</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5675</v>
+        <v>0.0515</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1095</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.458</v>
+        <v>0.1346</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1661</v>
+        <v>0.0614</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9785</v>
+        <v>0.0614</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1875</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5986</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.869</v>
+        <v>-0.1445</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2704</v>
+        <v>0.1346</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2084</v>
+        <v>-0.2744</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8335</v>
+        <v>-0.3225</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3748</v>
+        <v>0.0481</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2728</v>
+        <v>-2.2941</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3157</v>
+        <v>-2.4351</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0429</v>
+        <v>0.1409</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0515</v>
+        <v>-1.293</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-1.6432</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1346</v>
+        <v>0.3502</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0614</v>
+        <v>-0.3987</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0614</v>
+        <v>-1.6936</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.2949</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.8943</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1445</v>
+        <v>0.0504</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1346</v>
+        <v>-0.9447</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-2.3441</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5662</v>
+        <v>0.6082</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4237</v>
+        <v>0.0305</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1425</v>
+        <v>0.5777</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6468</v>
+        <v>-2.8583</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4351</v>
+        <v>-6.5421</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2118</v>
+        <v>3.6839</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.293</v>
+        <v>-4.2664</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6432</v>
+        <v>-1.6501</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3502</v>
+        <v>-2.6163</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3987</v>
+        <v>-5.1802</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.6936</v>
+        <v>-1.8906</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2949</v>
+        <v>-3.2896</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8943</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0504</v>
+        <v>0.2405</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9447</v>
+        <v>0.6733</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>-3.9069</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3441</v>
+        <v>-5.2743</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2555</v>
+        <v>1.6591</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0305</v>
+        <v>0.9206</v>
       </c>
       <c r="U21" t="n">
-        <v>0.225</v>
+        <v>0.7385</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2186</v>
+        <v>3.6559</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>2.9917</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2415</v>
+        <v>-4.0673</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.673</v>
+        <v>-4.5655</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5685</v>
+        <v>0.4983</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1285</v>
+        <v>-0.7771</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4538</v>
+        <v>0.1806</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6747</v>
+        <v>-0.9578</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6536</v>
+        <v>-1.5709</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6536</v>
+        <v>-0.3441</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.2268</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4749</v>
+        <v>0.7938</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1998</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6747</v>
+        <v>0.269</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3441</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4182</v>
+        <v>0.1239</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3247</v>
+        <v>-0.0645</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0935</v>
+        <v>0.1883</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3824</v>
+        <v>-2.4373</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3824</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6735</v>
+        <v>-5.2415</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5767</v>
+        <v>-2.673</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0968</v>
+        <v>-2.5685</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7771</v>
+        <v>-1.1285</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1806</v>
+        <v>-0.4538</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9578</v>
+        <v>-0.6747</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5709</v>
+        <v>-0.6536</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3441</v>
+        <v>-0.6536</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2268</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7938</v>
+        <v>-0.4749</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.1998</v>
       </c>
       <c r="O23" t="n">
-        <v>0.269</v>
+        <v>-0.6747</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>-2.3441</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4824</v>
+        <v>0.4182</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0756</v>
+        <v>0.3247</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4068</v>
+        <v>0.0935</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4373</v>
+        <v>-2.3824</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4373</v>
+        <v>-2.3824</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.8097</v>
+        <v>-5.4758</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.327199999999999</v>
+        <v>-7.3161</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5175</v>
+        <v>1.8403</v>
       </c>
       <c r="G24" t="n">
         <v>-6.5324</v>
@@ -2326,13 +2326,13 @@
         <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8633999999999999</v>
+        <v>0.4705</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9876</v>
+        <v>0.0236</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1242</v>
+        <v>0.4469</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-21.8736</v>
+        <v>-19.8514</v>
       </c>
       <c r="E25" t="n">
-        <v>-32.2036</v>
+        <v>-32.2035</v>
       </c>
       <c r="F25" t="n">
-        <v>10.3299</v>
+        <v>12.3523</v>
       </c>
       <c r="G25" t="n">
         <v>-10.4394</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.74</v>
+        <v>-7.739999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-2.6995</v>
@@ -2392,7 +2392,7 @@
         <v>2.5264</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6671</v>
+        <v>0.6670999999999998</v>
       </c>
       <c r="P25" t="n">
         <v>-7.813899999999999</v>
@@ -2404,13 +2404,13 @@
         <v>13.674</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1367</v>
+        <v>5.1592</v>
       </c>
       <c r="T25" t="n">
-        <v>1.308500000000001</v>
+        <v>1.3086</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8283</v>
+        <v>3.8505</v>
       </c>
       <c r="V25" t="n">
         <v>-6.757300000000001</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484326_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484326_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -860,6 +880,11 @@
       </c>
       <c r="X5" t="n">
         <v>0.3321</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,11 +1213,16 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1250,6 +1295,11 @@
       </c>
       <c r="X10" t="n">
         <v>-2.4373</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>1.3283</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-1.6085</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,11 +1707,16 @@
       <c r="X15" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0767</v>
+        <v>1.521</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4213</v>
+        <v>1.521</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3447</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5053</v>
+        <v>1.521</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4249</v>
+        <v>0.307</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0803</v>
+        <v>1.214</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1634</v>
+        <v>1.521</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2443</v>
+        <v>0.307</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0809</v>
+        <v>1.214</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6687</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6692</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0859</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1719</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1811,72 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5813</v>
+        <v>-0.0767</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3286</v>
+        <v>-1.4213</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7473</v>
+        <v>1.3447</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5185</v>
+        <v>0.5053</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4904</v>
+        <v>0.4249</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0089</v>
+        <v>0.0803</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1958</v>
+        <v>-0.1634</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5311</v>
+        <v>-0.2443</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3354</v>
+        <v>0.0809</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.6687</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0407</v>
+        <v>0.6692</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6735</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8612</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3675</v>
+        <v>-0.0859</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4937</v>
+        <v>0.1719</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.547</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.3283</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,11 +2039,16 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2941</v>
+        <v>-2.1022</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4351</v>
+        <v>-3.8496</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1409</v>
+        <v>1.7473</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.293</v>
+        <v>-1.0025</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6432</v>
+        <v>-1.7974</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3502</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3987</v>
+        <v>-1.7167</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6936</v>
+        <v>-1.8381</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2949</v>
+        <v>0.1214</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8943</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0504</v>
+        <v>0.0407</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9447</v>
+        <v>0.6735</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3441</v>
+        <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6082</v>
+        <v>0.8612</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0305</v>
+        <v>0.3675</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5777</v>
+        <v>0.4937</v>
       </c>
       <c r="V20" t="n">
+        <v>-2.547</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-1.3283</v>
+      </c>
+      <c r="X20" t="n">
         <v>-1.2186</v>
       </c>
-      <c r="W20" t="n">
-        <v>0.2772</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.4959</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8583</v>
+        <v>-2.2941</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.5421</v>
+        <v>-2.4351</v>
       </c>
       <c r="F21" t="n">
-        <v>3.6839</v>
+        <v>0.1409</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.2664</v>
+        <v>-1.293</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6501</v>
+        <v>-1.6432</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6163</v>
+        <v>0.3502</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.1802</v>
+        <v>-0.3987</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.8906</v>
+        <v>-1.6936</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.2896</v>
+        <v>1.2949</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9137999999999999</v>
+        <v>-0.8943</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2405</v>
+        <v>0.0504</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6733</v>
+        <v>-0.9447</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.9069</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.2743</v>
+        <v>-2.3441</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6591</v>
+        <v>0.6082</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9206</v>
+        <v>0.0305</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7385</v>
+        <v>0.5777</v>
       </c>
       <c r="V21" t="n">
-        <v>3.6559</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>2.9917</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6642</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0673</v>
+        <v>-2.8583</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.5655</v>
+        <v>-6.5421</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4983</v>
+        <v>3.6839</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7771</v>
+        <v>-4.2664</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1806</v>
+        <v>-1.6501</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9578</v>
+        <v>-2.6163</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5709</v>
+        <v>-5.1802</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3441</v>
+        <v>-1.8906</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2268</v>
+        <v>-3.2896</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7938</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.2405</v>
       </c>
       <c r="O22" t="n">
-        <v>0.269</v>
+        <v>0.6733</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-5.2743</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1239</v>
+        <v>1.6591</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0645</v>
+        <v>0.9206</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1883</v>
+        <v>0.7385</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4373</v>
+        <v>3.6559</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.9917</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2415</v>
+        <v>-4.0673</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.673</v>
+        <v>-4.5655</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5685</v>
+        <v>0.4983</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1285</v>
+        <v>-0.7771</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4538</v>
+        <v>0.1806</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6747</v>
+        <v>-0.9578</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6536</v>
+        <v>-1.5709</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6536</v>
+        <v>-0.3441</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.2268</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4749</v>
+        <v>0.7938</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1998</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6747</v>
+        <v>0.269</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3441</v>
+        <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4182</v>
+        <v>0.1239</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3247</v>
+        <v>-0.0645</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0935</v>
+        <v>0.1883</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.3824</v>
+        <v>-2.4373</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.3824</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. POPADIC</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4758</v>
+        <v>-5.2415</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.3161</v>
+        <v>-2.673</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8403</v>
+        <v>-2.5685</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.5324</v>
+        <v>-1.1285</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.4329</v>
+        <v>-0.4538</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.0995</v>
+        <v>-0.6747</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.1676</v>
+        <v>-0.6536</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.204</v>
+        <v>-0.6536</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.9637</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3647</v>
+        <v>-0.4749</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2289</v>
+        <v>0.1998</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1358</v>
+        <v>-0.6747</v>
       </c>
       <c r="P24" t="n">
-        <v>0.586</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1721</v>
+        <v>-2.3441</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4705</v>
+        <v>0.4182</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0236</v>
+        <v>0.3247</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4469</v>
+        <v>0.0935</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-2.3824</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.3824</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. POPADIC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-19.8514</v>
+        <v>-5.4758</v>
       </c>
       <c r="E25" t="n">
+        <v>-7.3161</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.8403</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-6.5324</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.4329</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-4.0995</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-6.1676</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-2.204</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-3.9637</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.3647</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.2289</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.1358</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.4705</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484326_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-19.8513</v>
+      </c>
+      <c r="E26" t="n">
         <v>-32.2035</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>12.3523</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>-10.4394</v>
       </c>
-      <c r="H25" t="n">
-        <v>-7.739999999999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-2.6995</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-13.6331</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="H26" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.699499999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-13.633</v>
+      </c>
+      <c r="K26" t="n">
         <v>-10.2664</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>-3.3666</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>3.1937</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.5264</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.6670999999999998</v>
-      </c>
-      <c r="P25" t="n">
-        <v>-7.813899999999999</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="N26" t="n">
+        <v>2.526400000000001</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.6671000000000002</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-7.8139</v>
+      </c>
+      <c r="Q26" t="n">
         <v>-21.4878</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>13.674</v>
       </c>
-      <c r="S25" t="n">
-        <v>5.1592</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="S26" t="n">
+        <v>5.159199999999999</v>
+      </c>
+      <c r="T26" t="n">
         <v>1.3086</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>3.8505</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>-6.757300000000001</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>1.6085</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-8.3658</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
